--- a/woorim.xlsx
+++ b/woorim.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6F7CD8-2EE2-448E-99B1-70DF9F994B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A54A530-5770-4BF0-9C4B-9F35AB1150F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-18150" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-18120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="woorim" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7259" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7268" uniqueCount="282">
   <si>
     <t/>
   </si>
@@ -184,6 +184,24 @@
     <t>기획1팀</t>
   </si>
   <si>
+    <t>선철수</t>
+  </si>
+  <si>
+    <t>김현숙</t>
+  </si>
+  <si>
+    <t>임동호</t>
+  </si>
+  <si>
+    <t>박종현B</t>
+  </si>
+  <si>
+    <t>이한미</t>
+  </si>
+  <si>
+    <t>이현지</t>
+  </si>
+  <si>
     <t>이혜수</t>
   </si>
   <si>
@@ -287,6 +305,18 @@
   </si>
   <si>
     <t>양미진</t>
+  </si>
+  <si>
+    <t>조하영</t>
+  </si>
+  <si>
+    <t>박상철</t>
+  </si>
+  <si>
+    <t>석민지</t>
+  </si>
+  <si>
+    <t>이주희</t>
   </si>
   <si>
     <t>김보경</t>
@@ -407,6 +437,9 @@
 셀피아팀</t>
   </si>
   <si>
+    <t>글러벌커머스</t>
+  </si>
+  <si>
     <t>이종일</t>
   </si>
   <si>
@@ -467,6 +500,9 @@
     <t>전종욱</t>
   </si>
   <si>
+    <t>이재욱</t>
+  </si>
+  <si>
     <t>오민선</t>
   </si>
   <si>
@@ -501,6 +537,12 @@
   </si>
   <si>
     <t>임지민</t>
+  </si>
+  <si>
+    <t>박민선</t>
+  </si>
+  <si>
+    <t>송지근</t>
   </si>
   <si>
     <t>한지혜</t>
@@ -827,63 +869,7 @@
     <t>서혜진</t>
   </si>
   <si>
-    <t>선철수</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>김현숙</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>임동호</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>박종현B</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>이한미</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>이현지</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>이주희</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>조하영</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>고대현</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>박상철</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>석민지</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>이재욱</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>박민선</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>송지근</t>
-    <phoneticPr fontId="130" type="noConversion"/>
-  </si>
-  <si>
-    <t>글러벌커머스</t>
+    <t>최하영</t>
     <phoneticPr fontId="130" type="noConversion"/>
   </si>
 </sst>
@@ -891,7 +877,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="132" x14ac:knownFonts="1">
+  <fonts count="131" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1931,12 +1917,6 @@
     <font>
       <sz val="8"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -3806,7 +3786,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4246,10 +4226,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4640,7 +4616,9 @@
       <c r="L2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="30"/>
+      <c r="M2" s="30" t="s">
+        <v>0</v>
+      </c>
       <c r="N2" s="30" t="s">
         <v>4</v>
       </c>
@@ -4913,7 +4891,9 @@
       <c r="L3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="31"/>
+      <c r="M3" s="31" t="s">
+        <v>0</v>
+      </c>
       <c r="N3" s="31" t="s">
         <v>0</v>
       </c>
@@ -5168,7 +5148,9 @@
       <c r="K4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="M4" s="32"/>
+      <c r="M4" s="32" t="s">
+        <v>0</v>
+      </c>
       <c r="N4" s="32" t="s">
         <v>0</v>
       </c>
@@ -5426,7 +5408,9 @@
       <c r="J5" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="44"/>
+      <c r="M5" s="44" t="s">
+        <v>0</v>
+      </c>
       <c r="N5" s="44" t="s">
         <v>12</v>
       </c>
@@ -5681,7 +5665,9 @@
       <c r="J6" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="M6" s="31"/>
+      <c r="M6" s="31" t="s">
+        <v>0</v>
+      </c>
       <c r="N6" s="31" t="s">
         <v>0</v>
       </c>
@@ -5921,7 +5907,9 @@
       <c r="J7" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="M7" s="32"/>
+      <c r="M7" s="32" t="s">
+        <v>0</v>
+      </c>
       <c r="N7" s="32" t="s">
         <v>0</v>
       </c>
@@ -6672,9 +6660,15 @@
       <c r="J10" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="K10" s="51"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="51"/>
+      <c r="K10" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="L10" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="M10" s="51" t="s">
+        <v>0</v>
+      </c>
       <c r="N10" s="51" t="s">
         <v>0</v>
       </c>
@@ -6890,32 +6884,32 @@
       <c r="D11" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="146" t="s">
-        <v>267</v>
-      </c>
-      <c r="G11" s="146" t="s">
-        <v>268</v>
-      </c>
-      <c r="H11" s="146" t="s">
-        <v>269</v>
-      </c>
-      <c r="J11" s="146" t="s">
-        <v>270</v>
-      </c>
-      <c r="K11" s="146" t="s">
-        <v>271</v>
+      <c r="E11" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="44" t="s">
+        <v>58</v>
       </c>
       <c r="L11" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="M11" s="146" t="s">
-        <v>272</v>
+      <c r="M11" s="44" t="s">
+        <v>59</v>
       </c>
       <c r="N11" s="44" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="P11" s="44" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="Q11" s="1" t="s">
         <v>0</v>
@@ -7020,7 +7014,7 @@
         <v>0</v>
       </c>
       <c r="AZ11" s="49" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="BA11" s="49" t="s">
         <v>0</v>
@@ -7035,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="BJ11" s="53" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="BK11" s="53" t="s">
         <v>0</v>
@@ -7175,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="33" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="T12" s="54" t="s">
         <v>0</v>
@@ -7193,7 +7187,7 @@
         <v>0</v>
       </c>
       <c r="Y12" s="33" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Z12" s="34" t="s">
         <v>0</v>
@@ -7217,7 +7211,7 @@
         <v>0</v>
       </c>
       <c r="AG12" s="50" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AH12" s="50" t="s">
         <v>0</v>
@@ -7226,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="AJ12" s="48" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AK12" s="48" t="s">
         <v>0</v>
@@ -7256,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="AX12" s="45" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="AY12" s="46" t="s">
         <v>0</v>
@@ -7265,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="BA12" s="45" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="BB12" s="46" t="s">
         <v>0</v>
@@ -7274,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="BD12" s="45" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="BE12" s="46" t="s">
         <v>0</v>
@@ -7283,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="BJ12" s="45" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="BK12" s="46" t="s">
         <v>0</v>
@@ -7292,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="BM12" s="45" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="BN12" s="46" t="s">
         <v>0</v>
@@ -7301,7 +7295,7 @@
         <v>0</v>
       </c>
       <c r="BR12" s="45" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="BS12" s="46" t="s">
         <v>0</v>
@@ -7310,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="BU12" s="45" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="BV12" s="46" t="s">
         <v>0</v>
@@ -7325,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="BZ12" s="45" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="CA12" s="46" t="s">
         <v>0</v>
@@ -7334,7 +7328,7 @@
         <v>0</v>
       </c>
       <c r="CC12" s="45" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="CD12" s="46" t="s">
         <v>0</v>
@@ -7343,7 +7337,7 @@
         <v>0</v>
       </c>
       <c r="CF12" s="45" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="CG12" s="46" t="s">
         <v>0</v>
@@ -7352,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="CK12" s="45" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="CL12" s="46" t="s">
         <v>0</v>
@@ -7361,7 +7355,7 @@
         <v>0</v>
       </c>
       <c r="CN12" s="45" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="CO12" s="46" t="s">
         <v>0</v>
@@ -7456,7 +7450,7 @@
         <v>0</v>
       </c>
       <c r="AF13" s="48" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AG13" s="48" t="s">
         <v>0</v>
@@ -7480,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="AP13" s="51" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AQ13" s="51" t="s">
         <v>0</v>
@@ -7495,7 +7489,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="45" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AV13" s="46" t="s">
         <v>0</v>
@@ -7504,7 +7498,7 @@
         <v>0</v>
       </c>
       <c r="AX13" s="45" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AY13" s="46" t="s">
         <v>0</v>
@@ -7513,7 +7507,7 @@
         <v>0</v>
       </c>
       <c r="BA13" s="45" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="BB13" s="46" t="s">
         <v>0</v>
@@ -7522,7 +7516,7 @@
         <v>0</v>
       </c>
       <c r="BD13" s="45" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="BE13" s="46" t="s">
         <v>0</v>
@@ -7540,7 +7534,7 @@
         <v>0</v>
       </c>
       <c r="BJ13" s="45" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="BK13" s="46" t="s">
         <v>0</v>
@@ -7549,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="BM13" s="45" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="BN13" s="46" t="s">
         <v>0</v>
@@ -7564,7 +7558,7 @@
         <v>0</v>
       </c>
       <c r="BR13" s="45" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="BS13" s="46" t="s">
         <v>0</v>
@@ -7573,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="BU13" s="45" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="BV13" s="46" t="s">
         <v>0</v>
@@ -7588,7 +7582,7 @@
         <v>0</v>
       </c>
       <c r="BZ13" s="45" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="CA13" s="46" t="s">
         <v>0</v>
@@ -7597,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="CC13" s="45" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="CD13" s="46" t="s">
         <v>0</v>
@@ -7606,7 +7600,7 @@
         <v>0</v>
       </c>
       <c r="CF13" s="45" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="CG13" s="46" t="s">
         <v>0</v>
@@ -7615,7 +7609,7 @@
         <v>0</v>
       </c>
       <c r="CK13" s="45" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="CL13" s="46" t="s">
         <v>0</v>
@@ -7644,34 +7638,34 @@
         <v>0</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E14" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="G14" s="146" t="s">
-        <v>274</v>
-      </c>
-      <c r="H14" s="146" t="s">
-        <v>275</v>
-      </c>
-      <c r="J14" s="146" t="s">
-        <v>276</v>
-      </c>
-      <c r="K14" s="146" t="s">
-        <v>277</v>
+      <c r="G14" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="44" t="s">
+        <v>97</v>
       </c>
       <c r="L14" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="M14" s="146" t="s">
-        <v>273</v>
+      <c r="M14" s="44" t="s">
+        <v>98</v>
       </c>
       <c r="N14" s="44" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P14" s="44" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>0</v>
@@ -7722,37 +7716,37 @@
         <v>0</v>
       </c>
       <c r="AG14" s="44" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="AH14" s="44" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="AI14" s="62" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="AJ14" s="44" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="AK14" s="44" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="AL14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AM14" s="44" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="AN14" s="44" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="AO14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AP14" s="44" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="AQ14" s="44" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="AR14" s="1" t="s">
         <v>0</v>
@@ -7776,7 +7770,7 @@
         <v>0</v>
       </c>
       <c r="AZ14" s="50" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BA14" s="50" t="s">
         <v>0</v>
@@ -7905,7 +7899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="8" t="s">
         <v>0</v>
       </c>
@@ -7924,7 +7918,6 @@
       <c r="H15" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="I15" s="147"/>
       <c r="J15" s="31" t="s">
         <v>0</v>
       </c>
@@ -8354,7 +8347,7 @@
         <v>0</v>
       </c>
       <c r="BJ16" s="63" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="BK16" s="64" t="s">
         <v>0</v>
@@ -8378,7 +8371,7 @@
         <v>0</v>
       </c>
       <c r="BR16" s="63" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="BS16" s="66" t="s">
         <v>0</v>
@@ -8500,7 +8493,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="33" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="T17" s="34" t="s">
         <v>0</v>
@@ -8518,7 +8511,7 @@
         <v>0</v>
       </c>
       <c r="Y17" s="33" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="Z17" s="34" t="s">
         <v>0</v>
@@ -8542,16 +8535,16 @@
         <v>0</v>
       </c>
       <c r="AG17" s="44" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AH17" s="44" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="AI17" s="62" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="AJ17" s="44" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="AK17" s="31" t="s">
         <v>0</v>
@@ -8560,16 +8553,16 @@
         <v>0</v>
       </c>
       <c r="AM17" s="44" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AN17" s="44" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="AO17" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AP17" s="44" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AQ17" s="44" t="s">
         <v>0</v>
@@ -8745,7 +8738,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="51" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="O18" s="51" t="s">
         <v>0</v>
@@ -8955,7 +8948,7 @@
         <v>0</v>
       </c>
       <c r="CF18" s="68" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="CG18" s="69" t="s">
         <v>0</v>
@@ -9008,13 +9001,13 @@
         <v>0</v>
       </c>
       <c r="N19" s="44" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="O19" s="18" t="s">
         <v>0</v>
       </c>
       <c r="P19" s="44" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="Q19" s="1" t="s">
         <v>0</v>
@@ -9119,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="AZ19" s="48" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BA19" s="48" t="s">
         <v>0</v>
@@ -9149,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="BJ19" s="48" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="BK19" s="48" t="s">
         <v>0</v>
@@ -9197,7 +9190,7 @@
         <v>0</v>
       </c>
       <c r="BZ19" s="49" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="CA19" s="49" t="s">
         <v>0</v>
@@ -9262,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="75" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="H20" s="76" t="s">
         <v>0</v>
@@ -9337,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="AM20" s="46" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AN20" s="46" t="s">
         <v>0</v>
@@ -9355,7 +9348,7 @@
         <v>0</v>
       </c>
       <c r="AU20" s="45" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="AV20" s="46" t="s">
         <v>0</v>
@@ -9364,7 +9357,7 @@
         <v>0</v>
       </c>
       <c r="AX20" s="45" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AY20" s="46" t="s">
         <v>0</v>
@@ -9373,7 +9366,7 @@
         <v>0</v>
       </c>
       <c r="BA20" s="45" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="BB20" s="46" t="s">
         <v>0</v>
@@ -9382,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="BD20" s="45" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BE20" s="46" t="s">
         <v>0</v>
@@ -9409,7 +9402,7 @@
         <v>0</v>
       </c>
       <c r="BM20" s="45" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="BN20" s="46" t="s">
         <v>0</v>
@@ -9418,7 +9411,7 @@
         <v>0</v>
       </c>
       <c r="BR20" s="45" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="BS20" s="46" t="s">
         <v>0</v>
@@ -9427,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="BU20" s="45" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="BV20" s="46" t="s">
         <v>0</v>
@@ -9439,7 +9432,7 @@
         <v>0</v>
       </c>
       <c r="BZ20" s="45" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="CA20" s="46" t="s">
         <v>0</v>
@@ -9448,7 +9441,7 @@
         <v>0</v>
       </c>
       <c r="CC20" s="45" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="CD20" s="46" t="s">
         <v>0</v>
@@ -9498,7 +9491,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="48" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D21" s="48" t="s">
         <v>0</v>
@@ -9507,7 +9500,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G21" s="51" t="s">
         <v>0</v>
@@ -9518,8 +9511,8 @@
       <c r="I21" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="J21" s="148" t="s">
-        <v>281</v>
+      <c r="J21" s="77" t="s">
+        <v>138</v>
       </c>
       <c r="K21" s="77" t="s">
         <v>0</v>
@@ -9588,16 +9581,16 @@
         <v>0</v>
       </c>
       <c r="AG21" s="44" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="AH21" s="44" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="AI21" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AJ21" s="44" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="AK21" s="44" t="s">
         <v>0</v>
@@ -9606,19 +9599,19 @@
         <v>0</v>
       </c>
       <c r="AM21" s="44" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="AN21" s="44" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="AO21" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AP21" s="44" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="AQ21" s="44" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="AR21" s="1" t="s">
         <v>0</v>
@@ -9630,7 +9623,7 @@
         <v>0</v>
       </c>
       <c r="AU21" s="45" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="AV21" s="46" t="s">
         <v>0</v>
@@ -9639,7 +9632,7 @@
         <v>0</v>
       </c>
       <c r="AX21" s="45" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="AY21" s="46" t="s">
         <v>0</v>
@@ -9648,7 +9641,7 @@
         <v>0</v>
       </c>
       <c r="BA21" s="45" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="BB21" s="46" t="s">
         <v>0</v>
@@ -9657,7 +9650,7 @@
         <v>0</v>
       </c>
       <c r="BD21" s="45" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="BE21" s="46" t="s">
         <v>0</v>
@@ -9675,7 +9668,7 @@
         <v>0</v>
       </c>
       <c r="BJ21" s="45" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="BK21" s="46" t="s">
         <v>0</v>
@@ -9684,7 +9677,7 @@
         <v>0</v>
       </c>
       <c r="BM21" s="45" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="BN21" s="46" t="s">
         <v>0</v>
@@ -9693,7 +9686,7 @@
         <v>0</v>
       </c>
       <c r="BR21" s="45" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="BS21" s="46" t="s">
         <v>0</v>
@@ -9702,7 +9695,7 @@
         <v>0</v>
       </c>
       <c r="BU21" s="45" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="BV21" s="46" t="s">
         <v>0</v>
@@ -9714,7 +9707,7 @@
         <v>0</v>
       </c>
       <c r="BZ21" s="45" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="CA21" s="46" t="s">
         <v>0</v>
@@ -9723,7 +9716,7 @@
         <v>0</v>
       </c>
       <c r="CC21" s="45" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="CD21" s="46" t="s">
         <v>0</v>
@@ -9776,16 +9769,16 @@
         <v>0</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="H22" s="44" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>0</v>
@@ -9793,20 +9786,20 @@
       <c r="J22" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="K22" s="146" t="s">
-        <v>278</v>
+      <c r="K22" s="44" t="s">
+        <v>159</v>
       </c>
       <c r="M22" s="44" t="s">
         <v>0</v>
       </c>
       <c r="N22" s="44" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="O22" s="18" t="s">
         <v>0</v>
       </c>
       <c r="P22" s="44" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="Q22" s="1" t="s">
         <v>0</v>
@@ -9818,7 +9811,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="69" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="U22" s="69" t="s">
         <v>0</v>
@@ -10383,16 +10376,16 @@
         <v>0</v>
       </c>
       <c r="AG24" s="44" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AH24" s="44" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="AI24" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AJ24" s="44" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="AK24" s="44" t="s">
         <v>0</v>
@@ -10404,16 +10397,16 @@
         <v>0</v>
       </c>
       <c r="AN24" s="44" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="AO24" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AP24" s="44" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="AQ24" s="44" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AR24" s="1" t="s">
         <v>0</v>
@@ -10565,16 +10558,16 @@
         <v>0</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G25" s="44" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H25" s="44" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="I25" s="18" t="s">
         <v>0</v>
@@ -10582,20 +10575,20 @@
       <c r="J25" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="K25" s="146" t="s">
-        <v>279</v>
-      </c>
-      <c r="M25" s="146" t="s">
-        <v>280</v>
+      <c r="K25" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="M25" s="44" t="s">
+        <v>173</v>
       </c>
       <c r="N25" s="44" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="O25" s="18" t="s">
         <v>0</v>
       </c>
       <c r="P25" s="44" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="Q25" s="1" t="s">
         <v>0</v>
@@ -10694,7 +10687,7 @@
         <v>0</v>
       </c>
       <c r="AX25" s="48" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="AY25" s="48" t="s">
         <v>0</v>
@@ -10721,7 +10714,7 @@
         <v>0</v>
       </c>
       <c r="BJ25" s="48" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="BK25" s="48" t="s">
         <v>0</v>
@@ -10769,7 +10762,7 @@
         <v>0</v>
       </c>
       <c r="BZ25" s="48" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="CA25" s="48" t="s">
         <v>0</v>
@@ -10954,7 +10947,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="45" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="AV26" s="46" t="s">
         <v>0</v>
@@ -10963,7 +10956,7 @@
         <v>0</v>
       </c>
       <c r="AX26" s="45" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="AY26" s="46" t="s">
         <v>0</v>
@@ -10972,7 +10965,7 @@
         <v>0</v>
       </c>
       <c r="BA26" s="45" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="BB26" s="46" t="s">
         <v>0</v>
@@ -10981,7 +10974,7 @@
         <v>0</v>
       </c>
       <c r="BD26" s="45" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="BE26" s="46" t="s">
         <v>0</v>
@@ -10999,7 +10992,7 @@
         <v>0</v>
       </c>
       <c r="BJ26" s="45" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="BK26" s="46" t="s">
         <v>0</v>
@@ -11008,7 +11001,7 @@
         <v>0</v>
       </c>
       <c r="BM26" s="45" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="BN26" s="46" t="s">
         <v>0</v>
@@ -11017,7 +11010,7 @@
         <v>0</v>
       </c>
       <c r="BR26" s="45" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="BS26" s="46" t="s">
         <v>0</v>
@@ -11041,7 +11034,7 @@
         <v>0</v>
       </c>
       <c r="BZ26" s="45" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="CA26" s="46" t="s">
         <v>0</v>
@@ -11050,7 +11043,7 @@
         <v>0</v>
       </c>
       <c r="CC26" s="45" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="CD26" s="46" t="s">
         <v>0</v>
@@ -11142,7 +11135,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="79" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="T27" s="72" t="s">
         <v>0</v>
@@ -11175,7 +11168,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="79" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="AE27" s="1" t="s">
         <v>0</v>
@@ -11271,7 +11264,7 @@
         <v>0</v>
       </c>
       <c r="BZ27" s="45" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="CA27" s="46" t="s">
         <v>0</v>
@@ -11280,7 +11273,7 @@
         <v>0</v>
       </c>
       <c r="CC27" s="45" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="CD27" s="46" t="s">
         <v>0</v>
@@ -11339,7 +11332,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="F28" s="48" t="s">
         <v>0</v>
@@ -11620,16 +11613,16 @@
         <v>0</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>0</v>
       </c>
       <c r="G29" s="44" t="s">
-        <v>171</v>
-      </c>
-      <c r="H29" s="44" t="s">
-        <v>0</v>
+        <v>185</v>
+      </c>
+      <c r="H29" s="146" t="s">
+        <v>281</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>0</v>
@@ -11710,7 +11703,7 @@
         <v>0</v>
       </c>
       <c r="AX29" s="33" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="AY29" s="34" t="s">
         <v>0</v>
@@ -11725,7 +11718,7 @@
         <v>0</v>
       </c>
       <c r="BC29" s="33" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="BD29" s="34" t="s">
         <v>0</v>
@@ -11755,7 +11748,7 @@
         <v>0</v>
       </c>
       <c r="BM29" s="33" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="BN29" s="34" t="s">
         <v>0</v>
@@ -12152,7 +12145,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="33" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="K31" s="34" t="s">
         <v>0</v>
@@ -12164,7 +12157,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="33" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="O31" s="34" t="s">
         <v>0</v>
@@ -12239,7 +12232,7 @@
         <v>0</v>
       </c>
       <c r="AM31" s="80" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="AN31" s="79" t="s">
         <v>0</v>
@@ -12248,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="AP31" s="36" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="AQ31" s="37" t="s">
         <v>0</v>
@@ -12418,19 +12411,19 @@
         <v>0</v>
       </c>
       <c r="D32" s="44" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>0</v>
       </c>
       <c r="G32" s="44" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="H32" s="44" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>0</v>
@@ -12649,7 +12642,7 @@
         <v>0</v>
       </c>
       <c r="CC32" s="45" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="CD32" s="46" t="s">
         <v>0</v>
@@ -12939,7 +12932,7 @@
         <v>0</v>
       </c>
       <c r="CE33" s="85" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="CF33" s="82" t="s">
         <v>0</v>
@@ -13333,7 +13326,7 @@
         <v>0</v>
       </c>
       <c r="X35" s="79" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="Y35" s="79" t="s">
         <v>0</v>
@@ -13408,7 +13401,7 @@
         <v>0</v>
       </c>
       <c r="AW35" s="79" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="AX35" s="79" t="s">
         <v>0</v>
@@ -13516,7 +13509,7 @@
         <v>0</v>
       </c>
       <c r="CG35" s="79" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="CH35" s="79" t="s">
         <v>0</v>
@@ -14714,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="99" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="H40" s="100" t="s">
         <v>0</v>
@@ -14747,7 +14740,7 @@
         <v>0</v>
       </c>
       <c r="R40" s="99" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="S40" s="100" t="s">
         <v>0</v>
@@ -14786,7 +14779,7 @@
         <v>0</v>
       </c>
       <c r="AE40" s="106" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="AF40" s="107" t="s">
         <v>0</v>
@@ -14918,7 +14911,7 @@
         <v>0</v>
       </c>
       <c r="BW40" s="99" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="BX40" s="100" t="s">
         <v>0</v>
@@ -14969,7 +14962,7 @@
         <v>0</v>
       </c>
       <c r="CN40" s="106" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="CO40" s="115" t="s">
         <v>0</v>
@@ -15850,7 +15843,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="99" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="H44" s="100" t="s">
         <v>0</v>
@@ -15871,7 +15864,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="99" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="O44" s="100" t="s">
         <v>0</v>
@@ -15922,7 +15915,7 @@
         <v>0</v>
       </c>
       <c r="AE44" s="106" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="AF44" s="107" t="s">
         <v>0</v>
@@ -16054,7 +16047,7 @@
         <v>0</v>
       </c>
       <c r="BW44" s="99" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="BX44" s="100" t="s">
         <v>0</v>
@@ -16066,7 +16059,7 @@
         <v>0</v>
       </c>
       <c r="CA44" s="87" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="CB44" s="88" t="s">
         <v>0</v>
@@ -16105,7 +16098,7 @@
         <v>0</v>
       </c>
       <c r="CN44" s="106" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="CO44" s="115" t="s">
         <v>0</v>
@@ -18176,7 +18169,7 @@
         <v>0</v>
       </c>
       <c r="X52" s="79" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="Y52" s="79" t="s">
         <v>0</v>
@@ -18233,7 +18226,7 @@
         <v>0</v>
       </c>
       <c r="AQ52" s="34" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="AR52" s="34" t="s">
         <v>0</v>
@@ -18254,13 +18247,13 @@
         <v>0</v>
       </c>
       <c r="AX52" s="80" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="AY52" s="123" t="s">
         <v>0</v>
       </c>
       <c r="AZ52" s="124" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="BA52" s="79" t="s">
         <v>0</v>
@@ -18293,7 +18286,7 @@
         <v>0</v>
       </c>
       <c r="BK52" s="33" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="BL52" s="34" t="s">
         <v>0</v>
@@ -18332,7 +18325,7 @@
         <v>0</v>
       </c>
       <c r="BX52" s="85" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="BY52" s="3" t="s">
         <v>0</v>
@@ -18356,7 +18349,7 @@
         <v>0</v>
       </c>
       <c r="CF52" s="79" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="CG52" s="79" t="s">
         <v>0</v>
@@ -18374,7 +18367,7 @@
         <v>0</v>
       </c>
       <c r="CL52" s="85" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="CM52" s="69" t="s">
         <v>0</v>
@@ -18920,19 +18913,19 @@
         <v>0</v>
       </c>
       <c r="X55" s="42" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="Y55" s="43" t="s">
         <v>0</v>
       </c>
       <c r="Z55" s="42" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="AA55" s="43" t="s">
         <v>0</v>
       </c>
       <c r="AB55" s="42" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="AC55" s="43" t="s">
         <v>0</v>
@@ -19055,7 +19048,7 @@
         <v>0</v>
       </c>
       <c r="BX55" s="33" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="BY55" s="34" t="s">
         <v>0</v>
@@ -19082,7 +19075,7 @@
         <v>0</v>
       </c>
       <c r="CG55" s="33" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="CH55" s="34" t="s">
         <v>0</v>
@@ -19097,7 +19090,7 @@
         <v>0</v>
       </c>
       <c r="CL55" s="71" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="CM55" s="72" t="s">
         <v>0</v>
@@ -19569,7 +19562,7 @@
         <v>0</v>
       </c>
       <c r="BK57" s="33" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="BL57" s="34" t="s">
         <v>0</v>
@@ -19712,7 +19705,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="49" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="W58" s="49" t="s">
         <v>0</v>
@@ -19727,7 +19720,7 @@
         <v>0</v>
       </c>
       <c r="AA58" s="48" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="AB58" s="48" t="s">
         <v>0</v>
@@ -19975,25 +19968,25 @@
         <v>0</v>
       </c>
       <c r="U59" s="126" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="V59" s="43" t="s">
         <v>0</v>
       </c>
       <c r="W59" s="42" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="X59" s="43" t="s">
         <v>0</v>
       </c>
       <c r="Y59" s="42" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="Z59" s="43" t="s">
         <v>0</v>
       </c>
       <c r="AA59" s="42" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="AB59" s="43" t="s">
         <v>0</v>
@@ -20501,25 +20494,25 @@
         <v>0</v>
       </c>
       <c r="U61" s="126" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="V61" s="43" t="s">
         <v>0</v>
       </c>
       <c r="W61" s="42" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="X61" s="43" t="s">
         <v>0</v>
       </c>
       <c r="Y61" s="42" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="Z61" s="43" t="s">
         <v>0</v>
       </c>
       <c r="AA61" s="42" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="AB61" s="43" t="s">
         <v>0</v>
@@ -20567,7 +20560,7 @@
         <v>0</v>
       </c>
       <c r="AQ61" s="34" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="AR61" s="34" t="s">
         <v>0</v>
@@ -20994,7 +20987,7 @@
         <v>0</v>
       </c>
       <c r="X63" s="50" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="Y63" s="50" t="s">
         <v>0</v>
@@ -21129,7 +21122,7 @@
         <v>0</v>
       </c>
       <c r="CL63" s="80" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="CM63" s="82" t="s">
         <v>0</v>
@@ -21221,7 +21214,7 @@
         <v>0</v>
       </c>
       <c r="Y64" s="49" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="Z64" s="49" t="s">
         <v>0</v>
@@ -21430,13 +21423,13 @@
         <v>0</v>
       </c>
       <c r="Y65" s="42" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="Z65" s="43" t="s">
         <v>0</v>
       </c>
       <c r="AA65" s="42" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="AB65" s="43" t="s">
         <v>0</v>
@@ -21756,7 +21749,7 @@
         <v>0</v>
       </c>
       <c r="BL66" s="42" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="BM66" s="43" t="s">
         <v>0</v>
@@ -21765,7 +21758,7 @@
         <v>0</v>
       </c>
       <c r="BO66" s="42" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="BP66" s="43" t="s">
         <v>0</v>
@@ -21774,7 +21767,7 @@
         <v>0</v>
       </c>
       <c r="BR66" s="42" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="BS66" s="43" t="s">
         <v>0</v>
@@ -21792,7 +21785,7 @@
         <v>0</v>
       </c>
       <c r="BY66" s="42" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="BZ66" s="43" t="s">
         <v>0</v>
@@ -21801,7 +21794,7 @@
         <v>0</v>
       </c>
       <c r="CB66" s="42" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="CC66" s="43" t="s">
         <v>0</v>
@@ -21819,7 +21812,7 @@
         <v>0</v>
       </c>
       <c r="CH66" s="138" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="CI66" s="125" t="s">
         <v>0</v>
@@ -21905,13 +21898,13 @@
         <v>0</v>
       </c>
       <c r="Y67" s="42" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="Z67" s="43" t="s">
         <v>0</v>
       </c>
       <c r="AA67" s="42" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="AB67" s="43" t="s">
         <v>0</v>
@@ -22297,7 +22290,7 @@
         <v>0</v>
       </c>
       <c r="BO68" s="42" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="BP68" s="43" t="s">
         <v>0</v>
@@ -22306,7 +22299,7 @@
         <v>0</v>
       </c>
       <c r="BR68" s="42" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="BS68" s="43" t="s">
         <v>0</v>
@@ -22315,7 +22308,7 @@
         <v>0</v>
       </c>
       <c r="BU68" s="42" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="BV68" s="43" t="s">
         <v>0</v>
@@ -22324,7 +22317,7 @@
         <v>0</v>
       </c>
       <c r="BY68" s="42" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="BZ68" s="43" t="s">
         <v>0</v>
@@ -22333,7 +22326,7 @@
         <v>0</v>
       </c>
       <c r="CB68" s="42" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="CC68" s="43" t="s">
         <v>0</v>
@@ -22342,7 +22335,7 @@
         <v>0</v>
       </c>
       <c r="CE68" s="42" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="CF68" s="126" t="s">
         <v>0</v>
@@ -22697,7 +22690,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="49" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="X70" s="49" t="s">
         <v>0</v>
@@ -22757,7 +22750,7 @@
         <v>0</v>
       </c>
       <c r="AQ70" s="34" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="AR70" s="34" t="s">
         <v>0</v>
@@ -22885,19 +22878,19 @@
         <v>0</v>
       </c>
       <c r="U71" s="126" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="V71" s="43" t="s">
         <v>0</v>
       </c>
       <c r="W71" s="42" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="X71" s="43" t="s">
         <v>0</v>
       </c>
       <c r="Y71" s="42" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="Z71" s="43" t="s">
         <v>0</v>
@@ -23014,7 +23007,7 @@
         <v>0</v>
       </c>
       <c r="BQ71" s="49" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="BR71" s="49" t="s">
         <v>0</v>
@@ -23026,7 +23019,7 @@
         <v>0</v>
       </c>
       <c r="CB71" s="49" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="CC71" s="49" t="s">
         <v>0</v>
@@ -23232,7 +23225,7 @@
         <v>0</v>
       </c>
       <c r="BL72" s="42" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="BM72" s="43" t="s">
         <v>0</v>
@@ -23241,7 +23234,7 @@
         <v>0</v>
       </c>
       <c r="BO72" s="42" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="BP72" s="43" t="s">
         <v>0</v>
@@ -23250,7 +23243,7 @@
         <v>0</v>
       </c>
       <c r="BR72" s="42" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="BS72" s="43" t="s">
         <v>0</v>
@@ -23259,7 +23252,7 @@
         <v>0</v>
       </c>
       <c r="BU72" s="42" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="BV72" s="43" t="s">
         <v>0</v>
@@ -23268,7 +23261,7 @@
         <v>0</v>
       </c>
       <c r="BY72" s="42" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="BZ72" s="43" t="s">
         <v>0</v>
@@ -23277,7 +23270,7 @@
         <v>0</v>
       </c>
       <c r="CB72" s="42" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="CC72" s="43" t="s">
         <v>0</v>
@@ -23286,7 +23279,7 @@
         <v>0</v>
       </c>
       <c r="CE72" s="42" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="CF72" s="43" t="s">
         <v>0</v>
@@ -23295,7 +23288,7 @@
         <v>0</v>
       </c>
       <c r="CH72" s="42" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="CI72" s="43" t="s">
         <v>0</v>
@@ -23369,25 +23362,25 @@
         <v>0</v>
       </c>
       <c r="U73" s="126" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="V73" s="43" t="s">
         <v>0</v>
       </c>
       <c r="W73" s="42" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="X73" s="43" t="s">
         <v>0</v>
       </c>
       <c r="Y73" s="42" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="Z73" s="43" t="s">
         <v>0</v>
       </c>
       <c r="AA73" s="42" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="AB73" s="136" t="s">
         <v>0</v>
@@ -23773,7 +23766,7 @@
         <v>0</v>
       </c>
       <c r="BO74" s="42" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="BP74" s="43" t="s">
         <v>0</v>
@@ -23782,7 +23775,7 @@
         <v>0</v>
       </c>
       <c r="BR74" s="42" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="BS74" s="43" t="s">
         <v>0</v>
@@ -23791,7 +23784,7 @@
         <v>0</v>
       </c>
       <c r="BU74" s="42" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="BV74" s="43" t="s">
         <v>0</v>
@@ -23803,7 +23796,7 @@
         <v>0</v>
       </c>
       <c r="BY74" s="42" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="BZ74" s="43" t="s">
         <v>0</v>
@@ -23812,7 +23805,7 @@
         <v>0</v>
       </c>
       <c r="CB74" s="42" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="CC74" s="43" t="s">
         <v>0</v>
@@ -23821,7 +23814,7 @@
         <v>0</v>
       </c>
       <c r="CE74" s="42" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="CF74" s="43" t="s">
         <v>0</v>
@@ -23913,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="X75" s="50" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="Y75" s="50" t="s">
         <v>0</v>
@@ -24302,7 +24295,7 @@
         <v>0</v>
       </c>
       <c r="CL76" s="33" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="CM76" s="34" t="s">
         <v>0</v>
@@ -24511,7 +24504,7 @@
         <v>0</v>
       </c>
       <c r="BR77" s="49" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="BS77" s="49" t="s">
         <v>0</v>
@@ -24520,7 +24513,7 @@
         <v>0</v>
       </c>
       <c r="CB77" s="49" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="CC77" s="49" t="s">
         <v>0</v>
@@ -24612,7 +24605,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="34" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="V78" s="34" t="s">
         <v>0</v>
@@ -24741,7 +24734,7 @@
         <v>0</v>
       </c>
       <c r="BO78" s="42" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="BP78" s="43" t="s">
         <v>0</v>
@@ -24750,7 +24743,7 @@
         <v>0</v>
       </c>
       <c r="BR78" s="42" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="BS78" s="43" t="s">
         <v>0</v>
@@ -24768,7 +24761,7 @@
         <v>0</v>
       </c>
       <c r="BY78" s="42" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="BZ78" s="43" t="s">
         <v>0</v>
@@ -24777,7 +24770,7 @@
         <v>0</v>
       </c>
       <c r="CB78" s="42" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="CC78" s="43" t="s">
         <v>0</v>
@@ -24786,7 +24779,7 @@
         <v>0</v>
       </c>
       <c r="CE78" s="42" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="CF78" s="43" t="s">
         <v>0</v>
@@ -24795,7 +24788,7 @@
         <v>0</v>
       </c>
       <c r="CH78" s="42" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="CI78" s="43" t="s">
         <v>0</v>
@@ -25285,7 +25278,7 @@
         <v>0</v>
       </c>
       <c r="BO80" s="42" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="BP80" s="43" t="s">
         <v>0</v>
@@ -25294,7 +25287,7 @@
         <v>0</v>
       </c>
       <c r="BR80" s="42" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="BS80" s="43" t="s">
         <v>0</v>
@@ -25303,7 +25296,7 @@
         <v>0</v>
       </c>
       <c r="BU80" s="42" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="BV80" s="43" t="s">
         <v>0</v>
@@ -25312,7 +25305,7 @@
         <v>0</v>
       </c>
       <c r="BY80" s="42" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="BZ80" s="43" t="s">
         <v>0</v>
@@ -25321,7 +25314,7 @@
         <v>0</v>
       </c>
       <c r="CB80" s="42" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="CC80" s="43" t="s">
         <v>0</v>
@@ -25330,7 +25323,7 @@
         <v>0</v>
       </c>
       <c r="CE80" s="42" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="CF80" s="43" t="s">
         <v>0</v>
@@ -26949,7 +26942,7 @@
   <phoneticPr fontId="130" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CV1 A12:CV13 A11:D11 F11 I11 L11 N11:CV11 A16:CV20 A14:F14 N14:CV14 I14 A15:H15 J15:CV15 L14 A23:CV24 A22:J22 L22:CV22 A26:CV86 A25:J25 L25 N25:CV25 A21:I21 K21:CV21 A10:J10 N10:CV10 A8:CV9 A2:L4 N2:CV4 A5:L7 N5:CV7" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CV28 A30:CV86 A29:G29 I29:CV29" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/woorim.xlsx
+++ b/woorim.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E74D5C-06AD-4765-90F5-E5195F0AE8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81905EC3-DE53-4C10-9DEF-891E57487B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="woorim" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7268" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7251" uniqueCount="277">
   <si>
     <t/>
   </si>
@@ -854,10 +859,6 @@
   </si>
   <si>
     <t>서혜진</t>
-  </si>
-  <si>
-    <t>이소정</t>
-    <phoneticPr fontId="129" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2423,7 +2424,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="121">
+  <borders count="122">
     <border>
       <left/>
       <right/>
@@ -3745,11 +3746,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4189,7 +4201,10 @@
     <xf numFmtId="0" fontId="128" fillId="104" borderId="120" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4532,12 +4547,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CQ86"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="100" width="5.33203125" customWidth="1"/>
+    <col min="1" max="100" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4548,7 +4563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -4832,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
         <v>0</v>
       </c>
@@ -5089,7 +5104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
         <v>0</v>
       </c>
@@ -5352,7 +5367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
         <v>0</v>
       </c>
@@ -5612,7 +5627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
         <v>0</v>
       </c>
@@ -5854,7 +5869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
         <v>0</v>
       </c>
@@ -6102,7 +6117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
         <v>0</v>
       </c>
@@ -6359,7 +6374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
         <v>0</v>
       </c>
@@ -6598,7 +6613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
         <v>0</v>
       </c>
@@ -6840,7 +6855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
         <v>0</v>
       </c>
@@ -7091,7 +7106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
         <v>0</v>
       </c>
@@ -7333,7 +7348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
         <v>0</v>
       </c>
@@ -7596,7 +7611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>0</v>
       </c>
@@ -7865,7 +7880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
         <v>0</v>
       </c>
@@ -8140,7 +8155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
         <v>0</v>
       </c>
@@ -8415,7 +8430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
         <v>0</v>
       </c>
@@ -8690,7 +8705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="8" t="s">
         <v>0</v>
       </c>
@@ -8950,7 +8965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="75" t="s">
         <v>0</v>
       </c>
@@ -9210,7 +9225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="75" t="s">
         <v>0</v>
       </c>
@@ -9452,7 +9467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="8" t="s">
         <v>0</v>
       </c>
@@ -9727,7 +9742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
         <v>0</v>
       </c>
@@ -9990,7 +10005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="8" t="s">
         <v>0</v>
       </c>
@@ -10198,24 +10213,14 @@
       <c r="BY23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BZ23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CA23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CB23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CC23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CD23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CE23" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="BZ23" s="147" t="s">
+        <v>123</v>
+      </c>
+      <c r="CA23" s="147"/>
+      <c r="CB23" s="147"/>
+      <c r="CC23" s="147"/>
+      <c r="CD23" s="147"/>
+      <c r="CE23" s="148"/>
       <c r="CF23" s="72" t="s">
         <v>0</v>
       </c>
@@ -10253,7 +10258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
         <v>0</v>
       </c>
@@ -10461,22 +10466,22 @@
       <c r="BY24" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BZ24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CA24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CB24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CC24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CD24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CE24" s="1" t="s">
+      <c r="BZ24" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="CA24" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="CB24" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="CC24" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="CD24" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="CE24" s="47" t="s">
         <v>0</v>
       </c>
       <c r="CF24" s="72" t="s">
@@ -10516,7 +10521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="8" t="s">
         <v>0</v>
       </c>
@@ -10727,22 +10732,22 @@
       <c r="BY25" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BZ25" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="CA25" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="CB25" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="CC25" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="CD25" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="CE25" s="49" t="s">
+      <c r="BZ25" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="CA25" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="CB25" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="CC25" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="CD25" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="CE25" s="47" t="s">
         <v>0</v>
       </c>
       <c r="CF25" s="72" t="s">
@@ -10782,7 +10787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="8" t="s">
         <v>0</v>
       </c>
@@ -10999,24 +11004,6 @@
       <c r="BY26" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BZ26" s="46" t="s">
-        <v>175</v>
-      </c>
-      <c r="CA26" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="CB26" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="CC26" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="CD26" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="CE26" s="47" t="s">
-        <v>0</v>
-      </c>
       <c r="CF26" s="72" t="s">
         <v>0</v>
       </c>
@@ -11054,7 +11041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="8" t="s">
         <v>0</v>
       </c>
@@ -11229,24 +11216,6 @@
       <c r="BY27" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BZ27" s="46" t="s">
-        <v>178</v>
-      </c>
-      <c r="CA27" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="CB27" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="CC27" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="CD27" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="CE27" s="47" t="s">
-        <v>0</v>
-      </c>
       <c r="CF27" s="72" t="s">
         <v>0</v>
       </c>
@@ -11284,7 +11253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
@@ -11571,7 +11540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -11807,7 +11776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
@@ -12088,7 +12057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -12369,7 +12338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -12653,7 +12622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -12937,7 +12906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
@@ -13221,7 +13190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
@@ -13508,7 +13477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
@@ -13795,7 +13764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
@@ -14082,7 +14051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -14369,7 +14338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -14656,7 +14625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="91" t="s">
         <v>0</v>
       </c>
@@ -14940,7 +14909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="94" t="s">
         <v>0</v>
       </c>
@@ -15224,7 +15193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="94" t="s">
         <v>0</v>
       </c>
@@ -15508,7 +15477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="94" t="s">
         <v>0</v>
       </c>
@@ -15792,7 +15761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="94" t="s">
         <v>0</v>
       </c>
@@ -16076,7 +16045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="94" t="s">
         <v>0</v>
       </c>
@@ -16360,7 +16329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="94" t="s">
         <v>0</v>
       </c>
@@ -16644,7 +16613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="97" t="s">
         <v>0</v>
       </c>
@@ -16928,7 +16897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="26" t="s">
         <v>0</v>
       </c>
@@ -17212,7 +17181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="26" t="s">
         <v>0</v>
       </c>
@@ -17496,7 +17465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="26" t="s">
         <v>0</v>
       </c>
@@ -17780,7 +17749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="26" t="s">
         <v>0</v>
       </c>
@@ -18064,7 +18033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
@@ -18351,7 +18320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>0</v>
       </c>
@@ -18578,7 +18547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>0</v>
       </c>
@@ -18808,7 +18777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>0</v>
       </c>
@@ -19074,7 +19043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>0</v>
       </c>
@@ -19340,7 +19309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>0</v>
       </c>
@@ -19606,7 +19575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
@@ -19872,7 +19841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>0</v>
       </c>
@@ -20138,7 +20107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>0</v>
       </c>
@@ -20398,7 +20367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>0</v>
       </c>
@@ -20658,7 +20627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>0</v>
       </c>
@@ -20882,7 +20851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>0</v>
       </c>
@@ -21106,7 +21075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>0</v>
       </c>
@@ -21315,7 +21284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>0</v>
       </c>
@@ -21524,7 +21493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>0</v>
       </c>
@@ -21790,7 +21759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>0</v>
       </c>
@@ -22056,7 +22025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>0</v>
       </c>
@@ -22322,7 +22291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>0</v>
       </c>
@@ -22588,7 +22557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
@@ -22782,7 +22751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>0</v>
       </c>
@@ -22861,8 +22830,8 @@
       <c r="Z71" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="AA71" s="147" t="s">
-        <v>277</v>
+      <c r="AA71" s="43" t="s">
+        <v>0</v>
       </c>
       <c r="AB71" s="44" t="s">
         <v>0</v>
@@ -23000,7 +22969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>0</v>
       </c>
@@ -23266,7 +23235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>0</v>
       </c>
@@ -23532,7 +23501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>0</v>
       </c>
@@ -23801,7 +23770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>0</v>
       </c>
@@ -24070,7 +24039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>0</v>
       </c>
@@ -24279,7 +24248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>0</v>
       </c>
@@ -24509,7 +24478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>0</v>
       </c>
@@ -24781,7 +24750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>0</v>
       </c>
@@ -25053,7 +25022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>0</v>
       </c>
@@ -25325,7 +25294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>0</v>
       </c>
@@ -25597,7 +25566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>0</v>
       </c>
@@ -25806,7 +25775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>0</v>
       </c>
@@ -26015,7 +25984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
@@ -26224,7 +26193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>0</v>
       </c>
@@ -26511,9 +26480,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:95" ht="25.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" spans="1:95" ht="26.1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="394">
+    <mergeCell ref="BZ23:CE23"/>
     <mergeCell ref="CL76:CQ85"/>
     <mergeCell ref="BR77:BT77"/>
     <mergeCell ref="CB77:CE77"/>
@@ -26690,7 +26660,6 @@
     <mergeCell ref="P25:P27"/>
     <mergeCell ref="AX25:BC25"/>
     <mergeCell ref="BJ25:BO25"/>
-    <mergeCell ref="BZ25:CE25"/>
     <mergeCell ref="AU26:AW26"/>
     <mergeCell ref="AX26:AZ26"/>
     <mergeCell ref="BA26:BC26"/>
@@ -26699,13 +26668,13 @@
     <mergeCell ref="BM26:BO26"/>
     <mergeCell ref="BR26:BT26"/>
     <mergeCell ref="BU26:BW26"/>
-    <mergeCell ref="BZ26:CB26"/>
-    <mergeCell ref="CC26:CE26"/>
+    <mergeCell ref="BZ24:CB24"/>
+    <mergeCell ref="CC24:CE24"/>
     <mergeCell ref="S27:S30"/>
     <mergeCell ref="AD27:AD30"/>
     <mergeCell ref="AX27:BC27"/>
-    <mergeCell ref="BZ27:CB27"/>
-    <mergeCell ref="CC27:CE27"/>
+    <mergeCell ref="BZ25:CB25"/>
+    <mergeCell ref="CC25:CE25"/>
     <mergeCell ref="BZ21:CB21"/>
     <mergeCell ref="CC21:CE21"/>
     <mergeCell ref="D22:D24"/>
@@ -26912,7 +26881,7 @@
   <phoneticPr fontId="129" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:CV70 A72:CV86 A71:Z71 AB71:CV71" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:CV22 A28:CV86 A25:BY27 CF25:CV27 A23:BY24 CF23:CV24" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>